--- a/data/trans_orig/P1804_2016_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1804_2016_2023-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17732</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24278</t>
+          <t>23710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45067</t>
+          <t>46697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>47806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77595</t>
+          <t>77932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380682</t>
+          <t>379988</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>401731</t>
+          <t>400777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>350688</t>
+          <t>349058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371477</t>
+          <t>372045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737623</t>
+          <t>737286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767621</t>
+          <t>767412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40823</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45920</t>
+          <t>45185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72784</t>
+          <t>73511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71026</t>
+          <t>71540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106959</t>
+          <t>106562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>549673</t>
+          <t>551245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>571465</t>
+          <t>571541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>490760</t>
+          <t>490033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517624</t>
+          <t>518359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1047081</t>
+          <t>1047478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1083014</t>
+          <t>1082500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>36717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74986</t>
+          <t>74883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68601</t>
+          <t>69430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106574</t>
+          <t>106033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>630736</t>
+          <t>632380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652067</t>
+          <t>652794</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>586400</t>
+          <t>586503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615946</t>
+          <t>616488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1223909</t>
+          <t>1224450</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1261882</t>
+          <t>1261053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46938</t>
+          <t>48117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30112</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54171</t>
+          <t>54569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>59380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93497</t>
+          <t>92028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599110</t>
+          <t>597931</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>623508</t>
+          <t>622233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>594906</t>
+          <t>594508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>618965</t>
+          <t>619354</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1201628</t>
+          <t>1203097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1237512</t>
+          <t>1235745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26993</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52033</t>
+          <t>51585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40215</t>
+          <t>40484</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69438</t>
+          <t>69173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75131</t>
+          <t>74889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116505</t>
+          <t>113630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425885</t>
+          <t>426333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>450925</t>
+          <t>451532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>427411</t>
+          <t>427676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>456634</t>
+          <t>456365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>858262</t>
+          <t>861137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>899636</t>
+          <t>899878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26621</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49632</t>
+          <t>51296</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31709</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>59016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65233</t>
+          <t>64441</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100680</t>
+          <t>99707</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284698</t>
+          <t>283034</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307709</t>
+          <t>307199</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>320152</t>
+          <t>318746</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>346053</t>
+          <t>344927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>611412</t>
+          <t>612385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>646859</t>
+          <t>647651</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>32836</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47382</t>
+          <t>46859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83217</t>
+          <t>80916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68822</t>
+          <t>67298</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109476</t>
+          <t>106846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>223586</t>
+          <t>224162</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>240513</t>
+          <t>241154</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>316952</t>
+          <t>319253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352787</t>
+          <t>353310</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>547691</t>
+          <t>550321</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>588345</t>
+          <t>589869</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>186939</t>
+          <t>184751</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>246481</t>
+          <t>243225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>322187</t>
+          <t>312856</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>391829</t>
+          <t>388852</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>520169</t>
+          <t>515476</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>614524</t>
+          <t>615517</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3147869</t>
+          <t>3151125</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3207411</t>
+          <t>3209599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3152713</t>
+          <t>3155690</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3222355</t>
+          <t>3231686</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6324368</t>
+          <t>6323375</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6418723</t>
+          <t>6423416</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16214</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>48271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28971</t>
+          <t>34668</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>20666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46884</t>
+          <t>54062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -3818,27 +3818,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396387</t>
+          <t>403565</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383773</t>
+          <t>382969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>285438</t>
+          <t>327446</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269326</t>
+          <t>309615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>295685</t>
+          <t>339160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>681825</t>
+          <t>731011</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>663912</t>
+          <t>711617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>694886</t>
+          <t>745013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310809</t>
+          <t>357886</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310809</t>
+          <t>357886</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310809</t>
+          <t>357886</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>710796</t>
+          <t>765679</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>710796</t>
+          <t>765679</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>710796</t>
+          <t>765679</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30165</t>
+          <t>36885</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>60165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47316</t>
+          <t>55478</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27478</t>
+          <t>41244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64920</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>77481</t>
+          <t>92363</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56564</t>
+          <t>69143</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104310</t>
+          <t>117622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>393382</t>
+          <t>440005</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374238</t>
+          <t>416725</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405465</t>
+          <t>455870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>464027</t>
+          <t>444688</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446423</t>
+          <t>427831</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483865</t>
+          <t>458922</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>857409</t>
+          <t>884693</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>830580</t>
+          <t>859434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>878326</t>
+          <t>907913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511343</t>
+          <t>500166</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511343</t>
+          <t>500166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511343</t>
+          <t>500166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934890</t>
+          <t>977056</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934890</t>
+          <t>977056</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934890</t>
+          <t>977056</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>42897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>49667</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33825</t>
+          <t>39091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>67743</t>
+          <t>78927</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53893</t>
+          <t>63070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84316</t>
+          <t>98350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>511040</t>
+          <t>591577</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497214</t>
+          <t>577940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520164</t>
+          <t>601685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>500023</t>
+          <t>572472</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>488469</t>
+          <t>561423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>508643</t>
+          <t>583048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1011063</t>
+          <t>1164049</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>994490</t>
+          <t>1144626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1024913</t>
+          <t>1179906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,67 +4734,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>49279</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18663</t>
+          <t>35022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65671</t>
+          <t>69050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>54501</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>44292</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>68403</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>7,4%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47917</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>36427</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>58205</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>89816</t>
+          <t>103780</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54288</t>
+          <t>86956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115604</t>
+          <t>125863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4847,67 +4847,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>845887</t>
+          <t>651338</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822115</t>
+          <t>631567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869123</t>
+          <t>665595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>90,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>682385</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>668483</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>692594</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>92,6%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>664964</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>654676</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>676454</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,28%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1510851</t>
+          <t>1333724</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1485063</t>
+          <t>1311641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1546379</t>
+          <t>1350548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38970</t>
+          <t>43862</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28820</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52340</t>
+          <t>57944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>44157</t>
+          <t>51359</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35599</t>
+          <t>41688</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54007</t>
+          <t>62857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>83127</t>
+          <t>95220</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69816</t>
+          <t>80473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99987</t>
+          <t>111451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>522264</t>
+          <t>565484</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>508894</t>
+          <t>551402</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>532414</t>
+          <t>576766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>502567</t>
+          <t>556273</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>492717</t>
+          <t>544775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>511125</t>
+          <t>565944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1024831</t>
+          <t>1121758</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1007971</t>
+          <t>1105527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1038142</t>
+          <t>1136505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546724</t>
+          <t>607632</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546724</t>
+          <t>607632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546724</t>
+          <t>607632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107958</t>
+          <t>1216978</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107958</t>
+          <t>1216978</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107958</t>
+          <t>1216978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>25504</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39986</t>
+          <t>43326</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>28755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53008</t>
+          <t>44478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>63623</t>
+          <t>69395</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>58881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86735</t>
+          <t>82772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>337390</t>
+          <t>373620</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328179</t>
+          <t>363754</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>345460</t>
+          <t>381576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>575521</t>
+          <t>403231</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>555360</t>
+          <t>394688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>595881</t>
+          <t>410411</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>912910</t>
+          <t>776851</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>889798</t>
+          <t>763474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>943393</t>
+          <t>787365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27302</t>
+          <t>29619</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>40453</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>32116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>50520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>56802</t>
+          <t>62046</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46399</t>
+          <t>51018</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>74746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>262633</t>
+          <t>288604</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255457</t>
+          <t>280579</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>268705</t>
+          <t>294680</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>388589</t>
+          <t>423560</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379343</t>
+          <t>413493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396051</t>
+          <t>431897</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>651222</t>
+          <t>712165</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>640212</t>
+          <t>699465</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>661625</t>
+          <t>723193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152011</t>
+          <t>189032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>226927</t>
+          <t>258774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>276729</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>228617</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>315698</t>
+          <t>351492</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>467563</t>
+          <t>536400</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>403907</t>
+          <t>491092</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>519745</t>
+          <t>584145</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3268983</t>
+          <t>3314195</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3232890</t>
+          <t>3273988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3307806</t>
+          <t>3343730</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3381129</t>
+          <t>3410056</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3342160</t>
+          <t>3376397</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3429241</t>
+          <t>3441815</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6650112</t>
+          <t>6724251</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6597930</t>
+          <t>6676506</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6713768</t>
+          <t>6769559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
